--- a/lean/docs/定理列表3.0.xlsx
+++ b/lean/docs/定理列表3.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\lyh\Mathematical-logic-project\lean\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lean4\project\Mathematical-logic-project\lean\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AEFDCE-EB06-4434-A51E-EED1704DD6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D7F805-4856-4454-B59F-46C7D3BEE517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-43" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="234">
   <si>
     <t>所属范围</t>
   </si>
@@ -1009,7 +1009,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1080,6 +1080,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1089,24 +1095,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1424,15 +1427,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:I80"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="16.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08203125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="66.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="175.77734375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="80.5546875" style="11" customWidth="1"/>
-    <col min="7" max="7" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="175.75" style="12" customWidth="1"/>
+    <col min="5" max="5" width="8.9140625" customWidth="1"/>
+    <col min="6" max="6" width="80.58203125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="25.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="14.4" customHeight="1" thickBot="1"/>
@@ -1460,8 +1463,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B3" s="30" t="s">
+    <row r="3" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B3" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="17" t="s">
@@ -1476,10 +1479,10 @@
       <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="26" t="s">
         <v>207</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -1487,7 +1490,7 @@
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="31"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="18" t="s">
         <v>212</v>
       </c>
@@ -1498,14 +1501,14 @@
         <v>185</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
       <c r="I4" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="31"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="18" t="s">
         <v>213</v>
       </c>
@@ -1516,14 +1519,14 @@
         <v>185</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
       <c r="I5" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="31"/>
+      <c r="B6" s="30"/>
       <c r="C6" s="18" t="s">
         <v>214</v>
       </c>
@@ -1534,14 +1537,14 @@
         <v>185</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="31"/>
+      <c r="B7" s="30"/>
       <c r="C7" s="18" t="s">
         <v>213</v>
       </c>
@@ -1552,14 +1555,14 @@
         <v>185</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
       <c r="I7" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B8" s="32"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="19" t="s">
         <v>215</v>
       </c>
@@ -1570,14 +1573,14 @@
         <v>185</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B9" s="30" t="s">
+    <row r="9" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B9" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -1590,10 +1593,10 @@
         <v>6</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="26" t="s">
         <v>207</v>
       </c>
       <c r="I9" s="4" t="s">
@@ -1601,7 +1604,7 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="31"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="18" t="s">
         <v>15</v>
       </c>
@@ -1612,14 +1615,14 @@
         <v>6</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
       <c r="I10" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="31"/>
+      <c r="B11" s="30"/>
       <c r="C11" s="18" t="s">
         <v>17</v>
       </c>
@@ -1630,14 +1633,14 @@
         <v>6</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
       <c r="I11" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="31"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="18" t="s">
         <v>19</v>
       </c>
@@ -1648,14 +1651,14 @@
         <v>6</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
       <c r="I12" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="31"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="18" t="s">
         <v>21</v>
       </c>
@@ -1666,14 +1669,14 @@
         <v>6</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="31"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="18" t="s">
         <v>23</v>
       </c>
@@ -1684,14 +1687,14 @@
         <v>6</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
       <c r="I14" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="31"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="18" t="s">
         <v>25</v>
       </c>
@@ -1702,14 +1705,14 @@
         <v>6</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
       <c r="I15" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B16" s="32"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="19" t="s">
         <v>27</v>
       </c>
@@ -1720,14 +1723,14 @@
         <v>6</v>
       </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
       <c r="I16" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B17" s="30" t="s">
+    <row r="17" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B17" s="29" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="17" t="s">
@@ -1740,10 +1743,10 @@
         <v>6</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="H17" s="27" t="s">
+      <c r="H17" s="32" t="s">
         <v>207</v>
       </c>
       <c r="I17" s="4" t="s">
@@ -1751,7 +1754,7 @@
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="31"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="18" t="s">
         <v>32</v>
       </c>
@@ -1762,14 +1765,14 @@
         <v>6</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="29"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="31"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="18" t="s">
         <v>34</v>
       </c>
@@ -1780,14 +1783,14 @@
         <v>6</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="29"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="33"/>
       <c r="I19" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B20" s="32"/>
+      <c r="B20" s="31"/>
       <c r="C20" s="19" t="s">
         <v>36</v>
       </c>
@@ -1800,14 +1803,14 @@
       <c r="F20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B21" s="30" t="s">
+    <row r="21" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B21" s="29" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="17" t="s">
@@ -1822,10 +1825,10 @@
       <c r="F21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="26" t="s">
         <v>207</v>
       </c>
       <c r="I21" s="5" t="s">
@@ -1833,7 +1836,7 @@
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="31"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="18" t="s">
         <v>44</v>
       </c>
@@ -1846,14 +1849,14 @@
       <c r="F22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="31"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="18" t="s">
         <v>46</v>
       </c>
@@ -1864,14 +1867,14 @@
         <v>6</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
       <c r="I23" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B24" s="32"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="19" t="s">
         <v>47</v>
       </c>
@@ -1884,14 +1887,14 @@
       <c r="F24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B25" s="30" t="s">
+    <row r="25" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B25" s="29" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="17" t="s">
@@ -1904,10 +1907,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="H25" s="24" t="s">
+      <c r="H25" s="26" t="s">
         <v>207</v>
       </c>
       <c r="I25" s="4" t="s">
@@ -1915,7 +1918,7 @@
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="31"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="18" t="s">
         <v>209</v>
       </c>
@@ -1926,14 +1929,14 @@
         <v>6</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
       <c r="I26" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="31"/>
+      <c r="B27" s="30"/>
       <c r="C27" s="18" t="s">
         <v>53</v>
       </c>
@@ -1944,14 +1947,14 @@
         <v>6</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
       <c r="I27" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="31"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="18" t="s">
         <v>55</v>
       </c>
@@ -1962,14 +1965,14 @@
         <v>6</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
       <c r="I28" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="31"/>
+      <c r="B29" s="30"/>
       <c r="C29" s="18" t="s">
         <v>57</v>
       </c>
@@ -1980,14 +1983,14 @@
         <v>6</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
       <c r="I29" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="31"/>
+      <c r="B30" s="30"/>
       <c r="C30" s="18" t="s">
         <v>59</v>
       </c>
@@ -2000,14 +2003,14 @@
       <c r="F30" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
       <c r="I30" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="31"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="18" t="s">
         <v>223</v>
       </c>
@@ -2018,14 +2021,14 @@
         <v>224</v>
       </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
       <c r="I31" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="31"/>
+      <c r="B32" s="30"/>
       <c r="C32" s="18" t="s">
         <v>227</v>
       </c>
@@ -2038,14 +2041,14 @@
       <c r="F32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
       <c r="I32" s="5" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="31"/>
+      <c r="B33" s="30"/>
       <c r="C33" s="18" t="s">
         <v>228</v>
       </c>
@@ -2058,14 +2061,14 @@
       <c r="F33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="I33" s="5" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="31"/>
+      <c r="B34" s="30"/>
       <c r="C34" s="18" t="s">
         <v>226</v>
       </c>
@@ -2076,18 +2079,18 @@
         <v>38</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
       <c r="I34" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="31"/>
+      <c r="B35" s="30"/>
       <c r="C35" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="24" t="s">
         <v>232</v>
       </c>
       <c r="E35" s="5" t="s">
@@ -2096,32 +2099,32 @@
       <c r="F35" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="31"/>
+      <c r="B36" s="30"/>
       <c r="C36" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="D36" s="34" t="s">
+      <c r="D36" s="25" t="s">
         <v>231</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>233</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
       <c r="I36" s="5" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B37" s="32"/>
+      <c r="B37" s="31"/>
       <c r="C37" s="19" t="s">
         <v>67</v>
       </c>
@@ -2134,14 +2137,14 @@
       <c r="F37" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
       <c r="I37" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B38" s="30" t="s">
+    <row r="38" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B38" s="29" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="17" t="s">
@@ -2156,14 +2159,14 @@
       <c r="F38" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="H38" s="24"/>
+      <c r="H38" s="26"/>
       <c r="I38" s="23"/>
     </row>
     <row r="39" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B39" s="32"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="19" t="s">
         <v>74</v>
       </c>
@@ -2174,12 +2177,12 @@
         <v>6</v>
       </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
       <c r="I39" s="22"/>
     </row>
-    <row r="40" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B40" s="30" t="s">
+    <row r="40" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B40" s="29" t="s">
         <v>76</v>
       </c>
       <c r="C40" s="17" t="s">
@@ -2194,14 +2197,18 @@
       <c r="F40" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="H40" s="24"/>
-      <c r="I40" s="23"/>
+      <c r="H40" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="I40" s="35" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="31"/>
+      <c r="B41" s="30"/>
       <c r="C41" s="18" t="s">
         <v>80</v>
       </c>
@@ -2212,12 +2219,14 @@
         <v>38</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="21"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="21" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="31"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="18" t="s">
         <v>82</v>
       </c>
@@ -2230,12 +2239,14 @@
       <c r="F42" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="21"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="21" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="43" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B43" s="32"/>
+      <c r="B43" s="31"/>
       <c r="C43" s="19" t="s">
         <v>85</v>
       </c>
@@ -2248,9 +2259,11 @@
       <c r="F43" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="22"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="22" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="44" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
       <c r="B44" s="2" t="s">
@@ -2272,8 +2285,8 @@
       <c r="H44" s="1"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B45" s="30" t="s">
+    <row r="45" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B45" s="29" t="s">
         <v>92</v>
       </c>
       <c r="C45" s="17" t="s">
@@ -2288,14 +2301,18 @@
       <c r="F45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="24" t="s">
+      <c r="G45" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="H45" s="24"/>
-      <c r="I45" s="23"/>
+      <c r="H45" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="I45" s="23" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="31"/>
+      <c r="B46" s="30"/>
       <c r="C46" s="18" t="s">
         <v>96</v>
       </c>
@@ -2306,12 +2323,14 @@
         <v>6</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="21"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="21" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="31"/>
+      <c r="B47" s="30"/>
       <c r="C47" s="18" t="s">
         <v>98</v>
       </c>
@@ -2322,12 +2341,14 @@
         <v>6</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="21"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="21" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="31"/>
+      <c r="B48" s="30"/>
       <c r="C48" s="18" t="s">
         <v>100</v>
       </c>
@@ -2338,12 +2359,14 @@
         <v>6</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="21"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="21" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="49" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B49" s="32"/>
+      <c r="B49" s="31"/>
       <c r="C49" s="19" t="s">
         <v>102</v>
       </c>
@@ -2354,9 +2377,11 @@
         <v>6</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="22"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="22" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="50" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
       <c r="B50" s="2" t="s">
@@ -2378,8 +2403,8 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B51" s="30" t="s">
+    <row r="51" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B51" s="29" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="17" t="s">
@@ -2392,14 +2417,18 @@
         <v>38</v>
       </c>
       <c r="F51" s="4"/>
-      <c r="G51" s="24" t="s">
+      <c r="G51" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="H51" s="24"/>
-      <c r="I51" s="23"/>
+      <c r="H51" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="31"/>
+      <c r="B52" s="30"/>
       <c r="C52" s="18" t="s">
         <v>111</v>
       </c>
@@ -2410,12 +2439,14 @@
         <v>38</v>
       </c>
       <c r="F52" s="5"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="21"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="21" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="53" spans="2:9">
-      <c r="B53" s="31"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="18" t="s">
         <v>113</v>
       </c>
@@ -2426,12 +2457,14 @@
         <v>38</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="21"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="21" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="54" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B54" s="32"/>
+      <c r="B54" s="31"/>
       <c r="C54" s="19" t="s">
         <v>115</v>
       </c>
@@ -2442,12 +2475,14 @@
         <v>38</v>
       </c>
       <c r="F54" s="3"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="22"/>
-    </row>
-    <row r="55" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B55" s="30" t="s">
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B55" s="29" t="s">
         <v>117</v>
       </c>
       <c r="C55" s="17" t="s">
@@ -2460,14 +2495,14 @@
         <v>38</v>
       </c>
       <c r="F55" s="4"/>
-      <c r="G55" s="24" t="s">
+      <c r="G55" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="H55" s="24"/>
+      <c r="H55" s="26"/>
       <c r="I55" s="23"/>
     </row>
     <row r="56" spans="2:9">
-      <c r="B56" s="31"/>
+      <c r="B56" s="30"/>
       <c r="C56" s="18" t="s">
         <v>120</v>
       </c>
@@ -2478,12 +2513,12 @@
         <v>38</v>
       </c>
       <c r="F56" s="5"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
       <c r="I56" s="21"/>
     </row>
     <row r="57" spans="2:9">
-      <c r="B57" s="31"/>
+      <c r="B57" s="30"/>
       <c r="C57" s="18" t="s">
         <v>122</v>
       </c>
@@ -2494,12 +2529,12 @@
         <v>38</v>
       </c>
       <c r="F57" s="5"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
       <c r="I57" s="21"/>
     </row>
     <row r="58" spans="2:9">
-      <c r="B58" s="31"/>
+      <c r="B58" s="30"/>
       <c r="C58" s="18" t="s">
         <v>124</v>
       </c>
@@ -2510,12 +2545,12 @@
         <v>38</v>
       </c>
       <c r="F58" s="5"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
       <c r="I58" s="21"/>
     </row>
     <row r="59" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B59" s="32"/>
+      <c r="B59" s="31"/>
       <c r="C59" s="19" t="s">
         <v>126</v>
       </c>
@@ -2526,12 +2561,12 @@
         <v>38</v>
       </c>
       <c r="F59" s="3"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="26"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
       <c r="I59" s="22"/>
     </row>
-    <row r="60" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B60" s="30" t="s">
+    <row r="60" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B60" s="29" t="s">
         <v>128</v>
       </c>
       <c r="C60" s="17" t="s">
@@ -2546,12 +2581,12 @@
       <c r="F60" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
       <c r="I60" s="23"/>
     </row>
     <row r="61" spans="2:9">
-      <c r="B61" s="31"/>
+      <c r="B61" s="30"/>
       <c r="C61" s="18" t="s">
         <v>132</v>
       </c>
@@ -2562,12 +2597,12 @@
         <v>6</v>
       </c>
       <c r="F61" s="5"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
       <c r="I61" s="21"/>
     </row>
     <row r="62" spans="2:9">
-      <c r="B62" s="31"/>
+      <c r="B62" s="30"/>
       <c r="C62" s="18" t="s">
         <v>134</v>
       </c>
@@ -2580,12 +2615,12 @@
       <c r="F62" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
       <c r="I62" s="21"/>
     </row>
     <row r="63" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B63" s="32"/>
+      <c r="B63" s="31"/>
       <c r="C63" s="19" t="s">
         <v>137</v>
       </c>
@@ -2598,12 +2633,12 @@
       <c r="F63" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
       <c r="I63" s="22"/>
     </row>
-    <row r="64" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B64" s="30" t="s">
+    <row r="64" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B64" s="29" t="s">
         <v>140</v>
       </c>
       <c r="C64" s="17" t="s">
@@ -2616,12 +2651,12 @@
         <v>38</v>
       </c>
       <c r="F64" s="4"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
       <c r="I64" s="23"/>
     </row>
     <row r="65" spans="2:9">
-      <c r="B65" s="31"/>
+      <c r="B65" s="30"/>
       <c r="C65" s="18" t="s">
         <v>143</v>
       </c>
@@ -2634,12 +2669,12 @@
       <c r="F65" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
       <c r="I65" s="21"/>
     </row>
     <row r="66" spans="2:9">
-      <c r="B66" s="31"/>
+      <c r="B66" s="30"/>
       <c r="C66" s="18" t="s">
         <v>146</v>
       </c>
@@ -2650,12 +2685,12 @@
         <v>38</v>
       </c>
       <c r="F66" s="5"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27"/>
       <c r="I66" s="21"/>
     </row>
     <row r="67" spans="2:9">
-      <c r="B67" s="31"/>
+      <c r="B67" s="30"/>
       <c r="C67" s="18" t="s">
         <v>148</v>
       </c>
@@ -2666,12 +2701,12 @@
         <v>6</v>
       </c>
       <c r="F67" s="5"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
       <c r="I67" s="21"/>
     </row>
     <row r="68" spans="2:9">
-      <c r="B68" s="31"/>
+      <c r="B68" s="30"/>
       <c r="C68" s="18" t="s">
         <v>150</v>
       </c>
@@ -2682,12 +2717,12 @@
         <v>6</v>
       </c>
       <c r="F68" s="5"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
       <c r="I68" s="21"/>
     </row>
     <row r="69" spans="2:9">
-      <c r="B69" s="31"/>
+      <c r="B69" s="30"/>
       <c r="C69" s="18" t="s">
         <v>152</v>
       </c>
@@ -2698,12 +2733,12 @@
         <v>6</v>
       </c>
       <c r="F69" s="5"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
       <c r="I69" s="21"/>
     </row>
     <row r="70" spans="2:9">
-      <c r="B70" s="31"/>
+      <c r="B70" s="30"/>
       <c r="C70" s="18" t="s">
         <v>154</v>
       </c>
@@ -2716,12 +2751,12 @@
       <c r="F70" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
       <c r="I70" s="21"/>
     </row>
     <row r="71" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B71" s="32"/>
+      <c r="B71" s="31"/>
       <c r="C71" s="19" t="s">
         <v>157</v>
       </c>
@@ -2734,12 +2769,12 @@
       <c r="F71" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="28"/>
       <c r="I71" s="22"/>
     </row>
-    <row r="72" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B72" s="30" t="s">
+    <row r="72" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B72" s="29" t="s">
         <v>186</v>
       </c>
       <c r="C72" s="17" t="s">
@@ -2752,12 +2787,12 @@
         <v>6</v>
       </c>
       <c r="F72" s="4"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="24"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
       <c r="I72" s="23"/>
     </row>
     <row r="73" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B73" s="32"/>
+      <c r="B73" s="31"/>
       <c r="C73" s="19" t="s">
         <v>162</v>
       </c>
@@ -2770,12 +2805,12 @@
       <c r="F73" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
       <c r="I73" s="21"/>
     </row>
-    <row r="74" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B74" s="30" t="s">
+    <row r="74" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B74" s="29" t="s">
         <v>165</v>
       </c>
       <c r="C74" s="17" t="s">
@@ -2790,12 +2825,12 @@
       <c r="F74" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="G74" s="24"/>
-      <c r="H74" s="27"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="32"/>
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B75" s="32"/>
+      <c r="B75" s="31"/>
       <c r="C75" s="19" t="s">
         <v>169</v>
       </c>
@@ -2808,12 +2843,12 @@
       <c r="F75" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G75" s="26"/>
-      <c r="H75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="34"/>
       <c r="I75" s="22"/>
     </row>
-    <row r="76" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B76" s="30" t="s">
+    <row r="76" spans="2:9" ht="14.5" thickBot="1">
+      <c r="B76" s="29" t="s">
         <v>172</v>
       </c>
       <c r="C76" s="17" t="s">
@@ -2828,12 +2863,12 @@
       <c r="F76" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
       <c r="I76" s="23"/>
     </row>
     <row r="77" spans="2:9">
-      <c r="B77" s="31"/>
+      <c r="B77" s="30"/>
       <c r="C77" s="18" t="s">
         <v>176</v>
       </c>
@@ -2844,12 +2879,12 @@
         <v>38</v>
       </c>
       <c r="F77" s="5"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
       <c r="I77" s="21"/>
     </row>
     <row r="78" spans="2:9">
-      <c r="B78" s="31"/>
+      <c r="B78" s="30"/>
       <c r="C78" s="18" t="s">
         <v>178</v>
       </c>
@@ -2860,12 +2895,12 @@
         <v>38</v>
       </c>
       <c r="F78" s="5"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
       <c r="I78" s="21"/>
     </row>
     <row r="79" spans="2:9">
-      <c r="B79" s="31"/>
+      <c r="B79" s="30"/>
       <c r="C79" s="18" t="s">
         <v>180</v>
       </c>
@@ -2876,12 +2911,12 @@
         <v>38</v>
       </c>
       <c r="F79" s="5"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
       <c r="I79" s="21"/>
     </row>
     <row r="80" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B80" s="32"/>
+      <c r="B80" s="31"/>
       <c r="C80" s="19" t="s">
         <v>182</v>
       </c>
@@ -2894,27 +2929,27 @@
       <c r="F80" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
+      <c r="G80" s="28"/>
+      <c r="H80" s="28"/>
       <c r="I80" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="G60:G63"/>
-    <mergeCell ref="G64:G71"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="G74:G75"/>
-    <mergeCell ref="G76:G80"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="G40:G43"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="G51:G54"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="G3:G8"/>
-    <mergeCell ref="G9:G16"/>
-    <mergeCell ref="G17:G20"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="G25:G37"/>
+    <mergeCell ref="H60:H63"/>
+    <mergeCell ref="H64:H71"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="H76:H80"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="H40:H43"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="H51:H54"/>
+    <mergeCell ref="H55:H59"/>
+    <mergeCell ref="H3:H8"/>
+    <mergeCell ref="H9:H16"/>
+    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="H25:H37"/>
     <mergeCell ref="B3:B8"/>
     <mergeCell ref="B9:B16"/>
     <mergeCell ref="B76:B80"/>
@@ -2930,21 +2965,21 @@
     <mergeCell ref="B51:B54"/>
     <mergeCell ref="B60:B63"/>
     <mergeCell ref="B64:B71"/>
-    <mergeCell ref="H3:H8"/>
-    <mergeCell ref="H9:H16"/>
-    <mergeCell ref="H17:H20"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="H25:H37"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="H40:H43"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="H51:H54"/>
-    <mergeCell ref="H55:H59"/>
-    <mergeCell ref="H60:H63"/>
-    <mergeCell ref="H64:H71"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="H76:H80"/>
+    <mergeCell ref="G3:G8"/>
+    <mergeCell ref="G9:G16"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="G25:G37"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="G40:G43"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="G51:G54"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="G60:G63"/>
+    <mergeCell ref="G64:G71"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="G74:G75"/>
+    <mergeCell ref="G76:G80"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2955,9 +2990,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C7CB644-0639-46D2-AED0-56A74AA80E6D}">
   <dimension ref="D3:F6"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/lean/docs/定理列表3.0.xlsx
+++ b/lean/docs/定理列表3.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\lyh\Mathematical-logic-project\lean\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AEFDCE-EB06-4434-A51E-EED1704DD6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F4D1D7-D4EE-4532-B4EA-93FA2E9D457F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22046" yWindow="-43" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="237">
   <si>
     <t>所属范围</t>
   </si>
@@ -377,33 +377,18 @@
     <t>房间级 BFS</t>
   </si>
   <si>
-    <t>first_hop_sound</t>
-  </si>
-  <si>
     <t>房间级 BFS 返回的第一跳方向，确实位于某条通往目标房间的合法路径上。</t>
   </si>
   <si>
-    <t>first_hop_respects_locked_exit</t>
-  </si>
-  <si>
     <t>在没有钥匙时，房间级 BFS 不会把尚未访问的锁门当作可通行边。</t>
   </si>
   <si>
-    <t>first_hop_shortest</t>
-  </si>
-  <si>
     <t>房间级 BFS 找到的第一跳属于最少房间跳数路径。</t>
   </si>
   <si>
-    <t>first_hop_complete</t>
-  </si>
-  <si>
     <t>若在当前已知房间图上确实存在一条合法房间路径，房间级 BFS 能返回对应第一跳。</t>
   </si>
   <si>
-    <t>first_hop_none_unreachable</t>
-  </si>
-  <si>
     <t>房间级 BFS 返回 None 时，表示在当前已知房间图中确实不存在合法路径。</t>
   </si>
   <si>
@@ -453,9 +438,6 @@
   </si>
   <si>
     <t>planner_navigation_safe</t>
-  </si>
-  <si>
-    <t>planner 经 GoToTile 产生的导航动作始终不越界、不撞已知墙、不进已知危险格，并通过 Shield 过滤。</t>
   </si>
   <si>
     <t>定理范围限于导航动作</t>
@@ -822,6 +804,41 @@
   </si>
   <si>
     <t>引理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意一个已经被假设静态安全的动作，经过 Shield 后仍静态安全，并满足条件式怪物安全。</t>
+  </si>
+  <si>
+    <t>DSLExecution.lean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现了抽象版本的证明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实现了单步的证明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allowed_fifo_total_first_hop_sound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allowed_fifo_total_respects_locked_exit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allowed_room_bfs_total_shortest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allowed_room_bfs_total_complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allowed_room_bfs_total_none_unreachable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1080,6 +1097,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1103,12 +1126,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1451,21 +1468,21 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="32" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>5</v>
@@ -1476,108 +1493,108 @@
       <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>207</v>
+      <c r="G3" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>201</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="31"/>
+      <c r="B4" s="33"/>
       <c r="C4" s="18" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
       <c r="I4" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="31"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="18" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
       <c r="I5" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="31"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="18" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
       <c r="I6" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="31"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="18" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
       <c r="I7" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B8" s="32"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="19" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="32" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="17" t="s">
@@ -1590,18 +1607,18 @@
         <v>6</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>207</v>
+      <c r="G9" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>201</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="31"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="18" t="s">
         <v>15</v>
       </c>
@@ -1612,14 +1629,14 @@
         <v>6</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
       <c r="I10" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="2:9">
-      <c r="B11" s="31"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="18" t="s">
         <v>17</v>
       </c>
@@ -1630,14 +1647,14 @@
         <v>6</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
       <c r="I11" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="31"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="18" t="s">
         <v>19</v>
       </c>
@@ -1648,14 +1665,14 @@
         <v>6</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
       <c r="I12" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="31"/>
+      <c r="B13" s="33"/>
       <c r="C13" s="18" t="s">
         <v>21</v>
       </c>
@@ -1666,14 +1683,14 @@
         <v>6</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="31"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="18" t="s">
         <v>23</v>
       </c>
@@ -1684,14 +1701,14 @@
         <v>6</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
       <c r="I14" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="31"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="18" t="s">
         <v>25</v>
       </c>
@@ -1702,14 +1719,14 @@
         <v>6</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
       <c r="I15" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B16" s="32"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="19" t="s">
         <v>27</v>
       </c>
@@ -1720,14 +1737,14 @@
         <v>6</v>
       </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
       <c r="I16" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="32" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="17" t="s">
@@ -1740,18 +1757,18 @@
         <v>6</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>207</v>
+      <c r="G17" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>201</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="2:9">
-      <c r="B18" s="31"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="18" t="s">
         <v>32</v>
       </c>
@@ -1762,14 +1779,14 @@
         <v>6</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="29"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="31"/>
       <c r="I18" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="31"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="18" t="s">
         <v>34</v>
       </c>
@@ -1780,14 +1797,14 @@
         <v>6</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="29"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="31"/>
       <c r="I19" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B20" s="32"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="19" t="s">
         <v>36</v>
       </c>
@@ -1800,14 +1817,14 @@
       <c r="F20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="32" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="17" t="s">
@@ -1822,23 +1839,23 @@
       <c r="F21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>207</v>
+      <c r="G21" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>201</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="31"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="18" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>38</v>
@@ -1846,37 +1863,37 @@
       <c r="F22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="31"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="18" t="s">
         <v>46</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
       <c r="I23" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B24" s="32"/>
+      <c r="B24" s="34"/>
       <c r="C24" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>6</v>
@@ -1884,14 +1901,14 @@
       <c r="F24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="32" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="17" t="s">
@@ -1904,20 +1921,20 @@
         <v>6</v>
       </c>
       <c r="F25" s="4"/>
-      <c r="G25" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>207</v>
+      <c r="G25" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>201</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="31"/>
+      <c r="B26" s="33"/>
       <c r="C26" s="18" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>52</v>
@@ -1926,14 +1943,14 @@
         <v>6</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
       <c r="I26" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="31"/>
+      <c r="B27" s="33"/>
       <c r="C27" s="18" t="s">
         <v>53</v>
       </c>
@@ -1944,14 +1961,14 @@
         <v>6</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
       <c r="I27" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="31"/>
+      <c r="B28" s="33"/>
       <c r="C28" s="18" t="s">
         <v>55</v>
       </c>
@@ -1962,14 +1979,14 @@
         <v>6</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
       <c r="I28" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="31"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="18" t="s">
         <v>57</v>
       </c>
@@ -1980,14 +1997,14 @@
         <v>6</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
       <c r="I29" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="31"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="18" t="s">
         <v>59</v>
       </c>
@@ -2000,34 +2017,34 @@
       <c r="F30" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
       <c r="I30" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="33"/>
+      <c r="C31" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="31"/>
-      <c r="C31" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>224</v>
-      </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
       <c r="I31" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="31"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="18" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>62</v>
@@ -2038,19 +2055,19 @@
       <c r="F32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
       <c r="I32" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="31"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="18" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>38</v>
@@ -2058,16 +2075,16 @@
       <c r="F33" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="I33" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="31"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="18" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>65</v>
@@ -2076,19 +2093,19 @@
         <v>38</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
       <c r="I34" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="31"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>232</v>
+        <v>202</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>226</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>38</v>
@@ -2096,32 +2113,32 @@
       <c r="F35" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
       <c r="I35" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="31"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="D36" s="34" t="s">
-        <v>231</v>
+        <v>224</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
       <c r="I36" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B37" s="32"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="19" t="s">
         <v>67</v>
       </c>
@@ -2134,14 +2151,14 @@
       <c r="F37" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
       <c r="I37" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="32" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="17" t="s">
@@ -2156,14 +2173,14 @@
       <c r="F38" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G38" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="H38" s="24"/>
+      <c r="G38" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="H38" s="26"/>
       <c r="I38" s="23"/>
     </row>
     <row r="39" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B39" s="32"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="19" t="s">
         <v>74</v>
       </c>
@@ -2174,12 +2191,12 @@
         <v>6</v>
       </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
       <c r="I39" s="22"/>
     </row>
     <row r="40" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="32" t="s">
         <v>76</v>
       </c>
       <c r="C40" s="17" t="s">
@@ -2194,14 +2211,14 @@
       <c r="F40" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G40" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="H40" s="24"/>
+      <c r="G40" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="H40" s="26"/>
       <c r="I40" s="23"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="31"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="18" t="s">
         <v>80</v>
       </c>
@@ -2212,12 +2229,12 @@
         <v>38</v>
       </c>
       <c r="F41" s="5"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
       <c r="I41" s="21"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="31"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="18" t="s">
         <v>82</v>
       </c>
@@ -2230,12 +2247,12 @@
       <c r="F42" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
       <c r="I42" s="21"/>
     </row>
     <row r="43" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B43" s="32"/>
+      <c r="B43" s="34"/>
       <c r="C43" s="19" t="s">
         <v>85</v>
       </c>
@@ -2248,8 +2265,8 @@
       <c r="F43" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
       <c r="I43" s="22"/>
     </row>
     <row r="44" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
@@ -2273,7 +2290,7 @@
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B45" s="30" t="s">
+      <c r="B45" s="32" t="s">
         <v>92</v>
       </c>
       <c r="C45" s="17" t="s">
@@ -2288,14 +2305,14 @@
       <c r="F45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="H45" s="24"/>
+      <c r="G45" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="H45" s="26"/>
       <c r="I45" s="23"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="31"/>
+      <c r="B46" s="33"/>
       <c r="C46" s="18" t="s">
         <v>96</v>
       </c>
@@ -2306,12 +2323,12 @@
         <v>6</v>
       </c>
       <c r="F46" s="5"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
       <c r="I46" s="21"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="31"/>
+      <c r="B47" s="33"/>
       <c r="C47" s="18" t="s">
         <v>98</v>
       </c>
@@ -2322,12 +2339,12 @@
         <v>6</v>
       </c>
       <c r="F47" s="5"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
       <c r="I47" s="21"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="31"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="18" t="s">
         <v>100</v>
       </c>
@@ -2338,12 +2355,12 @@
         <v>6</v>
       </c>
       <c r="F48" s="5"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
       <c r="I48" s="21"/>
     </row>
     <row r="49" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B49" s="32"/>
+      <c r="B49" s="34"/>
       <c r="C49" s="19" t="s">
         <v>102</v>
       </c>
@@ -2354,8 +2371,8 @@
         <v>6</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
       <c r="I49" s="22"/>
     </row>
     <row r="50" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
@@ -2379,7 +2396,7 @@
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B51" s="30" t="s">
+      <c r="B51" s="32" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="17" t="s">
@@ -2392,14 +2409,14 @@
         <v>38</v>
       </c>
       <c r="F51" s="4"/>
-      <c r="G51" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H51" s="24"/>
+      <c r="G51" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="H51" s="26"/>
       <c r="I51" s="23"/>
     </row>
     <row r="52" spans="2:9">
-      <c r="B52" s="31"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="18" t="s">
         <v>111</v>
       </c>
@@ -2410,12 +2427,12 @@
         <v>38</v>
       </c>
       <c r="F52" s="5"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
       <c r="I52" s="21"/>
     </row>
     <row r="53" spans="2:9">
-      <c r="B53" s="31"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="18" t="s">
         <v>113</v>
       </c>
@@ -2426,12 +2443,12 @@
         <v>38</v>
       </c>
       <c r="F53" s="5"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
       <c r="I53" s="21"/>
     </row>
     <row r="54" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B54" s="32"/>
+      <c r="B54" s="34"/>
       <c r="C54" s="19" t="s">
         <v>115</v>
       </c>
@@ -2442,460 +2459,472 @@
         <v>38</v>
       </c>
       <c r="F54" s="3"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="26"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
       <c r="I54" s="22"/>
     </row>
     <row r="55" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B55" s="30" t="s">
+      <c r="B55" s="32" t="s">
         <v>117</v>
       </c>
       <c r="C55" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="E55" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="H55" s="26"/>
+      <c r="I55" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" s="33"/>
+      <c r="C56" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="D56" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="H55" s="24"/>
-      <c r="I55" s="23"/>
-    </row>
-    <row r="56" spans="2:9">
-      <c r="B56" s="31"/>
-      <c r="C56" s="18" t="s">
+      <c r="E56" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="21"/>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" s="33"/>
+      <c r="C57" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="E57" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="21"/>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" s="33"/>
+      <c r="C58" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D58" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F56" s="5"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="21"/>
-    </row>
-    <row r="57" spans="2:9">
-      <c r="B57" s="31"/>
-      <c r="C57" s="18" t="s">
+      <c r="E58" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" s="5"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="21"/>
+    </row>
+    <row r="59" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
+      <c r="B59" s="34"/>
+      <c r="C59" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="E59" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="22"/>
+    </row>
+    <row r="60" spans="2:9" ht="14.4" thickBot="1">
+      <c r="B60" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="E57" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F57" s="5"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="21"/>
-    </row>
-    <row r="58" spans="2:9">
-      <c r="B58" s="31"/>
-      <c r="C58" s="18" t="s">
+      <c r="C60" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D60" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" s="5"/>
-      <c r="G58" s="25"/>
-      <c r="H58" s="25"/>
-      <c r="I58" s="21"/>
-    </row>
-    <row r="59" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B59" s="32"/>
-      <c r="C59" s="19" t="s">
+      <c r="E60" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="G60" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="H60" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="I60" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" s="33"/>
+      <c r="C61" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="E59" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="26"/>
-      <c r="I59" s="22"/>
-    </row>
-    <row r="60" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B60" s="30" t="s">
+      <c r="D61" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="E61" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="5"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="B62" s="33"/>
+      <c r="C62" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D62" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="E60" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" s="4" t="s">
+      <c r="E62" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="23"/>
-    </row>
-    <row r="61" spans="2:9">
-      <c r="B61" s="31"/>
-      <c r="C61" s="18" t="s">
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
+      <c r="B63" s="34"/>
+      <c r="C63" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D63" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E61" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="21"/>
-    </row>
-    <row r="62" spans="2:9">
-      <c r="B62" s="31"/>
-      <c r="C62" s="18" t="s">
+      <c r="E63" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="G63" s="28"/>
+      <c r="H63" s="28"/>
+      <c r="I63" s="22"/>
+    </row>
+    <row r="64" spans="2:9" ht="14.4" thickBot="1">
+      <c r="B64" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="C64" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="21"/>
-    </row>
-    <row r="63" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B63" s="32"/>
-      <c r="C63" s="19" t="s">
+      <c r="D64" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="E64" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="23"/>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="33"/>
+      <c r="C65" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F63" s="3" t="s">
+      <c r="D65" t="s">
+        <v>228</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="22"/>
-    </row>
-    <row r="64" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B64" s="30" t="s">
+      <c r="G65" s="27"/>
+      <c r="H65" s="27"/>
+      <c r="I65" s="21"/>
+    </row>
+    <row r="66" spans="2:9">
+      <c r="B66" s="33"/>
+      <c r="C66" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="D66" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="E66" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27"/>
+      <c r="I66" s="21"/>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="33"/>
+      <c r="C67" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="E64" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" s="4"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="23"/>
-    </row>
-    <row r="65" spans="2:9">
-      <c r="B65" s="31"/>
-      <c r="C65" s="18" t="s">
+      <c r="D67" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="E67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="21"/>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="B68" s="33"/>
+      <c r="C68" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E65" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F65" s="5" t="s">
+      <c r="D68" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="21"/>
-    </row>
-    <row r="66" spans="2:9">
-      <c r="B66" s="31"/>
-      <c r="C66" s="18" t="s">
+      <c r="E68" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F68" s="5"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="21"/>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="B69" s="33"/>
+      <c r="C69" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D69" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F66" s="5"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="21"/>
-    </row>
-    <row r="67" spans="2:9">
-      <c r="B67" s="31"/>
-      <c r="C67" s="18" t="s">
+      <c r="E69" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="21"/>
+    </row>
+    <row r="70" spans="2:9">
+      <c r="B70" s="33"/>
+      <c r="C70" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D70" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E67" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" s="5"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="21"/>
-    </row>
-    <row r="68" spans="2:9">
-      <c r="B68" s="31"/>
-      <c r="C68" s="18" t="s">
+      <c r="E70" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="21"/>
+    </row>
+    <row r="71" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
+      <c r="B71" s="34"/>
+      <c r="C71" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" s="5"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="21"/>
-    </row>
-    <row r="69" spans="2:9">
-      <c r="B69" s="31"/>
-      <c r="C69" s="18" t="s">
+      <c r="D71" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="E71" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="21"/>
-    </row>
-    <row r="70" spans="2:9">
-      <c r="B70" s="31"/>
-      <c r="C70" s="18" t="s">
+      <c r="G71" s="28"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="22"/>
+    </row>
+    <row r="72" spans="2:9" ht="14.4" thickBot="1">
+      <c r="B72" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D72" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F70" s="5" t="s">
+      <c r="E72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="23"/>
+    </row>
+    <row r="73" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
+      <c r="B73" s="34"/>
+      <c r="C73" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
-      <c r="I70" s="21"/>
-    </row>
-    <row r="71" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B71" s="32"/>
-      <c r="C71" s="19" t="s">
+      <c r="D73" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="E73" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F71" s="3" t="s">
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="21"/>
+    </row>
+    <row r="74" spans="2:9" ht="14.4" thickBot="1">
+      <c r="B74" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="22"/>
-    </row>
-    <row r="72" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B72" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="C72" s="17" t="s">
+      <c r="C74" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D74" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F72" s="4"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="24"/>
-      <c r="I72" s="23"/>
-    </row>
-    <row r="73" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B73" s="32"/>
-      <c r="C73" s="19" t="s">
+      <c r="E74" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="G74" s="26"/>
+      <c r="H74" s="29"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
+      <c r="B75" s="34"/>
+      <c r="C75" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E73" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F73" s="3" t="s">
+      <c r="D75" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="G73" s="26"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="21"/>
-    </row>
-    <row r="74" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B74" s="30" t="s">
+      <c r="E75" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="G75" s="28"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="22"/>
+    </row>
+    <row r="76" spans="2:9" ht="14.4" thickBot="1">
+      <c r="B76" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="C76" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" s="4" t="s">
+      <c r="D76" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G74" s="24"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B75" s="32"/>
-      <c r="C75" s="19" t="s">
+      <c r="E76" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="23"/>
+    </row>
+    <row r="77" spans="2:9">
+      <c r="B77" s="33"/>
+      <c r="C77" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" s="3" t="s">
+      <c r="D77" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="G75" s="26"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="22"/>
-    </row>
-    <row r="76" spans="2:9" ht="14.4" thickBot="1">
-      <c r="B76" s="30" t="s">
+      <c r="E77" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="21"/>
+    </row>
+    <row r="78" spans="2:9">
+      <c r="B78" s="33"/>
+      <c r="C78" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="D78" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="E78" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="21"/>
+    </row>
+    <row r="79" spans="2:9">
+      <c r="B79" s="33"/>
+      <c r="C79" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="E76" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F76" s="4" t="s">
+      <c r="D79" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="23"/>
-    </row>
-    <row r="77" spans="2:9">
-      <c r="B77" s="31"/>
-      <c r="C77" s="18" t="s">
+      <c r="E79" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="21"/>
+    </row>
+    <row r="80" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
+      <c r="B80" s="34"/>
+      <c r="C80" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D80" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="E77" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="25"/>
-      <c r="H77" s="25"/>
-      <c r="I77" s="21"/>
-    </row>
-    <row r="78" spans="2:9">
-      <c r="B78" s="31"/>
-      <c r="C78" s="18" t="s">
+      <c r="E80" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D78" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="21"/>
-    </row>
-    <row r="79" spans="2:9">
-      <c r="B79" s="31"/>
-      <c r="C79" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
-      <c r="I79" s="21"/>
-    </row>
-    <row r="80" spans="2:9" ht="14.4" customHeight="1" thickBot="1">
-      <c r="B80" s="32"/>
-      <c r="C80" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
+      <c r="G80" s="28"/>
+      <c r="H80" s="28"/>
       <c r="I80" s="22"/>
     </row>
   </sheetData>
@@ -2963,46 +2992,46 @@
   <sheetData>
     <row r="3" spans="4:6">
       <c r="D3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="4:6">
       <c r="D4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="4:6">
       <c r="D5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="4:6">
       <c r="D6" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E6" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
